--- a/exports/GVT&D_full_report.xlsx
+++ b/exports/GVT&D_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:U52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>9.85</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>132.5</v>
+        <v>125.6</v>
       </c>
       <c r="I2" t="n">
         <v>127.97941066291</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>0.57</v>
+        <v>-4.67</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>4.71</v>
       </c>
       <c r="M2" t="n">
-        <v>0.11</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.41</v>
+        <v>7.28</v>
       </c>
       <c r="O2" t="n">
         <v>0.5</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>10.28</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44651.55208333334</v>
+        <v>44652.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>91.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="I3" t="n">
         <v>93.46717114862729</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>66.16666666666667</v>
+        <v>67</v>
       </c>
       <c r="K3" t="n">
-        <v>27.47</v>
+        <v>22.53</v>
       </c>
       <c r="L3" t="n">
         <v>4.66</v>
@@ -612,7 +647,7 @@
         <v>5.33</v>
       </c>
       <c r="N3" t="n">
-        <v>5.33</v>
+        <v>6.53</v>
       </c>
       <c r="O3" t="n">
         <v>-7.28</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.98</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44686.38541666666</v>
+        <v>44686.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>116.75</v>
+        <v>113.9</v>
       </c>
       <c r="I4" t="n">
         <v>114.01865230966</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>19.99</v>
+        <v>17.06</v>
       </c>
       <c r="L4" t="n">
         <v>6.47</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.22</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44749.38541666666</v>
+        <v>44749.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>100.3</v>
+        <v>102.7</v>
       </c>
       <c r="I5" t="n">
         <v>102.3204595514407</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>62.83333333333334</v>
+        <v>63</v>
       </c>
       <c r="K5" t="n">
-        <v>11.94</v>
+        <v>9.83</v>
       </c>
       <c r="L5" t="n">
         <v>2.5</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44831.38541666666</v>
+        <v>44831.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>127.85</v>
+        <v>125.2</v>
       </c>
       <c r="I6" t="n">
         <v>126.0792030091081</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>81.83333333333333</v>
+        <v>82</v>
       </c>
       <c r="K6" t="n">
-        <v>24.49</v>
+        <v>21.91</v>
       </c>
       <c r="L6" t="n">
         <v>3.55</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.23</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44937.38541666666</v>
+        <v>44937.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>119.1</v>
+        <v>124.5</v>
       </c>
       <c r="I7" t="n">
         <v>119.7844668928872</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>105.8333333333333</v>
+        <v>106</v>
       </c>
       <c r="K7" t="n">
-        <v>4.87</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L7" t="n">
         <v>14.66</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>10.22</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44978.55208333334</v>
+        <v>44979.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>113.6</v>
+        <v>110.9</v>
       </c>
       <c r="I8" t="n">
         <v>111.7791213627479</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>41</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.76</v>
+        <v>-10.92</v>
       </c>
       <c r="L8" t="n">
-        <v>9.640000000000001</v>
+        <v>11.33</v>
       </c>
       <c r="M8" t="n">
         <v>2.48</v>
       </c>
       <c r="N8" t="n">
-        <v>3.61</v>
+        <v>4.58</v>
       </c>
       <c r="O8" t="n">
         <v>5.51</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44993.38541666666</v>
+        <v>44993.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>112.1</v>
+        <v>113.75</v>
       </c>
       <c r="I9" t="n">
         <v>113.5327256509922</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.08</v>
+        <v>-2.57</v>
       </c>
       <c r="L9" t="n">
-        <v>3.2</v>
+        <v>5.77</v>
       </c>
       <c r="M9" t="n">
         <v>2.42</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,25 +1109,25 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45069.55208333334</v>
+        <v>45070.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>208.7</v>
+        <v>198.3</v>
       </c>
       <c r="I10" t="n">
         <v>200.456605057479</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>76</v>
+        <v>76.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>83.47</v>
+        <v>74.33</v>
       </c>
       <c r="L10" t="n">
         <v>1.45</v>
       </c>
       <c r="M10" t="n">
-        <v>1.53</v>
+        <v>4.98</v>
       </c>
       <c r="N10" t="n">
         <v>5.57</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>16.83</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45083.55208333334</v>
+        <v>45084.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>197.95</v>
+        <v>207.9</v>
       </c>
       <c r="I11" t="n">
         <v>200.8143571463195</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>0.18</v>
+        <v>-4.84</v>
       </c>
       <c r="L11" t="n">
-        <v>0.18</v>
+        <v>4.84</v>
       </c>
       <c r="M11" t="n">
         <v>2.25</v>
       </c>
       <c r="N11" t="n">
-        <v>4.62</v>
+        <v>5.03</v>
       </c>
       <c r="O11" t="n">
         <v>-4.98</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>13.78</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45168.38541666666</v>
+        <v>45168.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>324.6</v>
+        <v>320</v>
       </c>
       <c r="I12" t="n">
         <v>323.8005999130277</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>84</v>
+        <v>84.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>56.13</v>
+        <v>53.92</v>
       </c>
       <c r="L12" t="n">
         <v>6.2</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>13.8</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45182.55208333334</v>
+        <v>45183.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>345.1</v>
+        <v>358</v>
       </c>
       <c r="I13" t="n">
         <v>355.0965894590803</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.84</v>
+        <v>-11.88</v>
       </c>
       <c r="L13" t="n">
-        <v>10.27</v>
+        <v>13.19</v>
       </c>
       <c r="M13" t="n">
         <v>2.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.08</v>
+        <v>4.87</v>
       </c>
       <c r="O13" t="n">
         <v>-2.79</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>13.68</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45205.55208333334</v>
+        <v>45208.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>404.25</v>
+        <v>394.4</v>
       </c>
       <c r="I14" t="n">
         <v>394.753211522503</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K14" t="n">
-        <v>12.92</v>
+        <v>10.17</v>
       </c>
       <c r="L14" t="n">
         <v>3.95</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>13.01</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45251.38541666666</v>
+        <v>45251.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>403.1</v>
+        <v>415</v>
       </c>
       <c r="I15" t="n">
         <v>406.3715636075118</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>43</v>
+        <v>43.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.21</v>
+        <v>-5.22</v>
       </c>
       <c r="L15" t="n">
         <v>5.58</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>11.04</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45364.55208333334</v>
+        <v>45365.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>907.85</v>
+        <v>862.5</v>
       </c>
       <c r="I16" t="n">
         <v>866.94723981629</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>113</v>
+        <v>113.8333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>118.76</v>
+        <v>107.83</v>
       </c>
       <c r="L16" t="n">
         <v>5.06</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>16.01</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45385.55208333334</v>
+        <v>45386.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>925.45</v>
+        <v>970</v>
       </c>
       <c r="I17" t="n">
         <v>950.7399657249264</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.3</v>
+        <v>-12.46</v>
       </c>
       <c r="L17" t="n">
-        <v>7.3</v>
+        <v>12.59</v>
       </c>
       <c r="M17" t="n">
-        <v>1.71</v>
+        <v>2.14</v>
       </c>
       <c r="N17" t="n">
-        <v>3.42</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
         <v>-4.17</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>13.09</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45420.38541666666</v>
+        <v>45420.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>1062</v>
+        <v>1038.35</v>
       </c>
       <c r="I18" t="n">
         <v>1039.262460174746</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K18" t="n">
-        <v>9.48</v>
+        <v>7.05</v>
       </c>
       <c r="L18" t="n">
         <v>11.36</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,25 +1730,25 @@
         <v>15.9</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45426.55208333334</v>
+        <v>45427.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1086.9</v>
+        <v>1133.45</v>
       </c>
       <c r="I19" t="n">
         <v>1133.070167705704</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.68</v>
+        <v>-9.16</v>
       </c>
       <c r="L19" t="n">
-        <v>5.07</v>
+        <v>9.16</v>
       </c>
       <c r="M19" t="n">
-        <v>0.58</v>
+        <v>2.13</v>
       </c>
       <c r="N19" t="n">
         <v>4.51</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>14.17</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1285</v>
+        <v>1250</v>
       </c>
       <c r="I20" t="n">
         <v>1272.285465002592</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>13.37</v>
+        <v>10.28</v>
       </c>
       <c r="L20" t="n">
         <v>3.83</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>14.99</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45453.55208333334</v>
+        <v>45454.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1375</v>
+        <v>1443.45</v>
       </c>
       <c r="I21" t="n">
         <v>1413.576033355371</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>-10</v>
+        <v>-15.48</v>
       </c>
       <c r="L21" t="n">
-        <v>14.27</v>
+        <v>16.32</v>
       </c>
       <c r="M21" t="n">
         <v>4.94</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>12.42</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1590</v>
+        <v>1515.35</v>
       </c>
       <c r="I22" t="n">
         <v>1521.478132828654</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K22" t="n">
-        <v>10.15</v>
+        <v>4.98</v>
       </c>
       <c r="L22" t="n">
         <v>6.14</v>
@@ -1695,7 +1958,7 @@
         <v>2.73</v>
       </c>
       <c r="N22" t="n">
-        <v>3.57</v>
+        <v>4.69</v>
       </c>
       <c r="O22" t="n">
         <v>4</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>14.43</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45503.38541666666</v>
+        <v>45503.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>1575</v>
+        <v>1625</v>
       </c>
       <c r="I23" t="n">
         <v>1593.36786757718</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.94</v>
+        <v>-7.24</v>
       </c>
       <c r="L23" t="n">
-        <v>5.59</v>
+        <v>8.49</v>
       </c>
       <c r="M23" t="n">
         <v>0.68</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>12.96</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45539.38541666666</v>
+        <v>45539.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>1649.7</v>
+        <v>1629.95</v>
       </c>
       <c r="I24" t="n">
         <v>1636.494712766749</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>35.83333333333334</v>
+        <v>36</v>
       </c>
       <c r="K24" t="n">
-        <v>1.52</v>
+        <v>0.3</v>
       </c>
       <c r="L24" t="n">
         <v>4.49</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>9.67</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45562.38541666666</v>
+        <v>45562.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>1652.15</v>
+        <v>1705.75</v>
       </c>
       <c r="I25" t="n">
         <v>1699.131952459695</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.36</v>
+        <v>-4.65</v>
       </c>
       <c r="L25" t="n">
         <v>10.92</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>11.06</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45586.55208333334</v>
+        <v>45587.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1768.9</v>
+        <v>1715</v>
       </c>
       <c r="I26" t="n">
         <v>1735.212819905527</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>3.7</v>
+        <v>0.54</v>
       </c>
       <c r="L26" t="n">
         <v>7.5</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>12.74</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45607.55208333334</v>
+        <v>45608.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1777.15</v>
+        <v>1866</v>
       </c>
       <c r="I27" t="n">
         <v>1845.602995609319</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.62</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>7.74</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>6.1</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>11.72</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1997</v>
+        <v>1955.9</v>
       </c>
       <c r="I28" t="n">
         <v>1965.135973150038</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K28" t="n">
-        <v>7.02</v>
+        <v>4.82</v>
       </c>
       <c r="L28" t="n">
         <v>9.34</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>8.99</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45727.38541666666</v>
+        <v>45727.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>1446.2</v>
+        <v>1475.5</v>
       </c>
       <c r="I29" t="n">
         <v>1457.535502729081</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>60</v>
+        <v>60.16666666666666</v>
       </c>
       <c r="K29" t="n">
-        <v>26.06</v>
+        <v>24.56</v>
       </c>
       <c r="L29" t="n">
         <v>2.15</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.77</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1480.85</v>
+        <v>1436.95</v>
       </c>
       <c r="I30" t="n">
         <v>1454.893525086075</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>21</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>0.36</v>
+        <v>-2.61</v>
       </c>
       <c r="L30" t="n">
         <v>4.83</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>13.47</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45763.38541666666</v>
+        <v>45763.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>1389.8</v>
+        <v>1461</v>
       </c>
       <c r="I31" t="n">
         <v>1443.392530378324</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>3.28</v>
+        <v>-1.67</v>
       </c>
       <c r="L31" t="n">
         <v>3.36</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>12.64</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45894.55208333334</v>
+        <v>45895.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>2744.9</v>
+        <v>2705</v>
       </c>
       <c r="I32" t="n">
         <v>2721.409189002994</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>131</v>
+        <v>131.8333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>87.88</v>
+        <v>85.15000000000001</v>
       </c>
       <c r="L32" t="n">
         <v>5.11</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>7.07</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45912.55208333334</v>
+        <v>45915.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>2786</v>
+        <v>2854.9</v>
       </c>
       <c r="I33" t="n">
         <v>2845.256181950721</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.99</v>
+        <v>-5.54</v>
       </c>
       <c r="L33" t="n">
-        <v>5.36</v>
+        <v>5.54</v>
       </c>
       <c r="M33" t="n">
         <v>1.73</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45944.55208333334</v>
+        <v>45945.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>2965</v>
+        <v>2939.7</v>
       </c>
       <c r="I34" t="n">
         <v>2951.045481872561</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K34" t="n">
-        <v>3.86</v>
+        <v>2.97</v>
       </c>
       <c r="L34" t="n">
         <v>3.39</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>7.61</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45959.38541666666</v>
+        <v>45959.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>2995.7</v>
+        <v>3069</v>
       </c>
       <c r="I35" t="n">
         <v>3063.748036175276</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.9</v>
+        <v>-4.4</v>
       </c>
       <c r="L35" t="n">
-        <v>3.23</v>
+        <v>4.8</v>
       </c>
       <c r="M35" t="n">
         <v>1.2</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45981.55208333334</v>
+        <v>45982.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>3061</v>
+        <v>2886.4</v>
       </c>
       <c r="I36" t="n">
         <v>2930.476528622051</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.26</v>
+        <v>-5.95</v>
       </c>
       <c r="L36" t="n">
-        <v>3.16</v>
+        <v>6.61</v>
       </c>
       <c r="M36" t="n">
         <v>1.48</v>
       </c>
       <c r="N36" t="n">
-        <v>4.4</v>
+        <v>5.33</v>
       </c>
       <c r="O36" t="n">
         <v>3.96</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.32</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46002.38541666666</v>
+        <v>46002.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>2920.3</v>
+        <v>3012</v>
       </c>
       <c r="I37" t="n">
         <v>2987.200951348809</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.17</v>
+        <v>-4.35</v>
       </c>
       <c r="L37" t="n">
         <v>5.81</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.37</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>2983.1</v>
+        <v>2876.5</v>
       </c>
       <c r="I38" t="n">
         <v>2944.526855297913</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.96</v>
+        <v>-4.5</v>
       </c>
       <c r="L38" t="n">
         <v>6.95</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.77</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46049.55208333334</v>
+        <v>46050.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>2741.4</v>
+        <v>2880.3</v>
       </c>
       <c r="I39" t="n">
         <v>2789.553136253053</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K39" t="n">
-        <v>4.7</v>
+        <v>-0.13</v>
       </c>
       <c r="L39" t="n">
         <v>3.6</v>
@@ -2664,7 +3131,7 @@
         <v>1.33</v>
       </c>
       <c r="N39" t="n">
-        <v>4.16</v>
+        <v>6.15</v>
       </c>
       <c r="O39" t="n">
         <v>-2.45</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>11.51</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46094.55208333334</v>
+        <v>46097.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>3640</v>
+        <v>3464.2</v>
       </c>
       <c r="I40" t="n">
         <v>3601.336190947506</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K40" t="n">
-        <v>26.38</v>
+        <v>20.27</v>
       </c>
       <c r="L40" t="n">
         <v>5.39</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>10.73</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46099.38541666666</v>
+        <v>46099.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>3770</v>
+        <v>3838.6</v>
       </c>
       <c r="I41" t="n">
         <v>3825.145803010977</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>-8.83</v>
+        <v>-10.81</v>
       </c>
       <c r="L41" t="n">
-        <v>9.76</v>
+        <v>10.96</v>
       </c>
       <c r="M41" t="n">
         <v>1.18</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>10.22</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46101.55208333334</v>
+        <v>46104.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>3685</v>
+        <v>3436.8</v>
       </c>
       <c r="I42" t="n">
         <v>3449.936572280048</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>-4</v>
+        <v>-10.47</v>
       </c>
       <c r="L42" t="n">
-        <v>5.05</v>
+        <v>10.9</v>
       </c>
       <c r="M42" t="n">
         <v>1.82</v>
       </c>
       <c r="N42" t="n">
-        <v>2.24</v>
+        <v>5.59</v>
       </c>
       <c r="O42" t="n">
         <v>4.97</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>14.07</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46111.55208333334</v>
+        <v>46113.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>3670</v>
+        <v>3841.5</v>
       </c>
       <c r="I43" t="n">
         <v>3839.892141434355</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.79</v>
+        <v>-11.78</v>
       </c>
       <c r="L43" t="n">
-        <v>11.34</v>
+        <v>26.4</v>
       </c>
       <c r="M43" t="n">
         <v>3.62</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.51</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46150.55208333334</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>4630</v>
+        <v>4458.7</v>
       </c>
       <c r="I44" t="n">
         <v>4468.094473344611</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K44" t="n">
-        <v>20.53</v>
+        <v>16.07</v>
       </c>
       <c r="L44" t="n">
         <v>4.99</v>
@@ -2949,7 +3476,7 @@
         <v>2.25</v>
       </c>
       <c r="N44" t="n">
-        <v>3.32</v>
+        <v>4.32</v>
       </c>
       <c r="O44" t="n">
         <v>3.53</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>9.68</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46161.55208333334</v>
+        <v>46162.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>4357.6</v>
+        <v>4694.8</v>
       </c>
       <c r="I45" t="n">
         <v>4653.691336491266</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
-        <v>2.27</v>
+        <v>-5.3</v>
       </c>
       <c r="L45" t="n">
-        <v>3.95</v>
+        <v>7.65</v>
       </c>
       <c r="M45" t="n">
-        <v>0.25</v>
+        <v>2.12</v>
       </c>
       <c r="N45" t="n">
-        <v>1.81</v>
+        <v>7.63</v>
       </c>
       <c r="O45" t="n">
         <v>-4.32</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>12.11</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46174.55208333334</v>
+        <v>46175.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>4750</v>
+        <v>4584.5</v>
       </c>
       <c r="I46" t="n">
         <v>4688.524823505164</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K46" t="n">
-        <v>1.18</v>
+        <v>-2.35</v>
       </c>
       <c r="L46" t="n">
         <v>5.97</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>15.32</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46190.55208333334</v>
+        <v>46191.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>5130</v>
+        <v>5213</v>
       </c>
       <c r="I47" t="n">
         <v>5188.917788846017</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K47" t="n">
-        <v>-11.9</v>
+        <v>-13.71</v>
       </c>
       <c r="L47" t="n">
-        <v>12.9</v>
+        <v>14.3</v>
       </c>
       <c r="M47" t="n">
         <v>3.3</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>10.47</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46198.55208333334</v>
+        <v>46202.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>5050</v>
+        <v>4939</v>
       </c>
       <c r="I48" t="n">
         <v>5009.293902510792</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.13</v>
+        <v>-5.26</v>
       </c>
       <c r="L48" t="n">
-        <v>4.75</v>
+        <v>9.43</v>
       </c>
       <c r="M48" t="n">
         <v>1.73</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>10.79</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46260.55208333334</v>
+        <v>46261.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>4350</v>
+        <v>4408.7</v>
       </c>
       <c r="I49" t="n">
         <v>4350.758562640511</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>58.16666666666666</v>
+        <v>59</v>
       </c>
       <c r="K49" t="n">
-        <v>11.93</v>
+        <v>10.74</v>
       </c>
       <c r="L49" t="n">
         <v>2.83</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.86</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46276.55208333334</v>
+        <v>46280.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>4518.8</v>
+        <v>4317.5</v>
       </c>
       <c r="I50" t="n">
         <v>4450.655664325192</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K50" t="n">
-        <v>2.5</v>
+        <v>-2.07</v>
       </c>
       <c r="L50" t="n">
         <v>5.11</v>
@@ -3291,7 +3890,7 @@
         <v>0.9</v>
       </c>
       <c r="N50" t="n">
-        <v>2.77</v>
+        <v>6.42</v>
       </c>
       <c r="O50" t="n">
         <v>0.65</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46321.55208333334</v>
+        <v>46322.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>3768</v>
+        <v>4014.9</v>
       </c>
       <c r="I51" t="n">
         <v>3908.620529340794</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K51" t="n">
-        <v>12.73</v>
+        <v>7.01</v>
       </c>
       <c r="L51" t="n">
         <v>4.69</v>
@@ -3348,7 +3959,7 @@
         <v>1.29</v>
       </c>
       <c r="N51" t="n">
-        <v>3.16</v>
+        <v>6.15</v>
       </c>
       <c r="O51" t="n">
         <v>-6.42</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3408,6 +4031,12 @@
       <c r="Q52" t="n">
         <v>2</v>
       </c>
+      <c r="R52" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5510,7 +6139,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -5520,7 +6149,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="7">
@@ -5530,7 +6159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>131</v>
+        <v>131.8</v>
       </c>
     </row>
     <row r="8">
@@ -5540,7 +6169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -5550,7 +6179,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>42.5</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +6189,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -5600,7 +6229,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10.34</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="15">
@@ -5610,7 +6239,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19.49</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="16">
@@ -5620,7 +6249,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.19</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="17">
@@ -5630,7 +6259,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>118.76</v>
+        <v>107.83</v>
       </c>
     </row>
     <row r="18">
@@ -5640,7 +6269,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
@@ -5650,7 +6279,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.92</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="20">
@@ -5660,7 +6289,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.09</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="21">
@@ -5670,7 +6299,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.66</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="22">
@@ -5680,7 +6309,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -5690,7 +6319,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -5700,7 +6329,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.51</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="25">
@@ -5720,7 +6349,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.68</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="27">
@@ -5740,7 +6369,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29">
